--- a/dados/dados_brutos_transfermarkt.xlsx
+++ b/dados/dados_brutos_transfermarkt.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Elenco_2014" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Elenco_2015" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Elenco_2016" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Elenco_2017" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Elenco_2018" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Elenco_2019" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Elenco_2020" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Elenco_2021" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Elenco_2022" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Elenco_2023" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Elenco_2024" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Elenco_2025" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Pontos_2014" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Pontos_2015" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Pontos_2016" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Pontos_2017" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Pontos_2018" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Pontos_2019" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Pontos_2020" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Pontos_2021" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Pontos_2022" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Pontos_2023" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Pontos_2024" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2014" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2015" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2016" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2017" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2018" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2019" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2020" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2021" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2022" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2023" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2024" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elenco_2025" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2014" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2015" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2016" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2017" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2018" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2019" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2020" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2021" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2022" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2023" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontos_2024" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9633,16 +9633,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.463</v>
+        <v>0.448</v>
       </c>
       <c r="F17" t="n">
         <v>28.7</v>
